--- a/analysis/econometrics_outputs/sdid/Graficos/contracts/sdid_levels_cosine_nearest_top_vs_zero.xlsx
+++ b/analysis/econometrics_outputs/sdid/Graficos/contracts/sdid_levels_cosine_nearest_top_vs_zero.xlsx
@@ -507,13 +507,13 @@
         <v>2876.168</v>
       </c>
       <c r="I2" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J2" t="n">
-        <v>-204.5673586811945</v>
+        <v>-449.2447152788297</v>
       </c>
       <c r="K2" t="n">
-        <v>428.1735522295813</v>
+        <v>672.8509088272165</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>2575.836</v>
       </c>
       <c r="I3" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J3" t="n">
-        <v>18.69206067364388</v>
+        <v>-225.9852959239913</v>
       </c>
       <c r="K3" t="n">
-        <v>651.4329715844196</v>
+        <v>896.1103281820549</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>3112.868</v>
       </c>
       <c r="I4" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J4" t="n">
-        <v>-206.3238102940975</v>
+        <v>-451.0011668917327</v>
       </c>
       <c r="K4" t="n">
-        <v>426.4171006166783</v>
+        <v>671.0944572143135</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>3040.771999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J5" t="n">
-        <v>-170.0826490037746</v>
+        <v>-414.7600056014098</v>
       </c>
       <c r="K5" t="n">
-        <v>462.6582619070012</v>
+        <v>707.3356185046364</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +679,13 @@
         <v>3465.04</v>
       </c>
       <c r="I6" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J6" t="n">
-        <v>-489.8667780360332</v>
+        <v>-734.5441346336684</v>
       </c>
       <c r="K6" t="n">
-        <v>142.8741328747427</v>
+        <v>387.5514894723779</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>4192.092000000002</v>
       </c>
       <c r="I7" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J7" t="n">
-        <v>-777.9752296489387</v>
+        <v>-1022.652586246574</v>
       </c>
       <c r="K7" t="n">
-        <v>-145.2343187381629</v>
+        <v>99.44303785947227</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +765,13 @@
         <v>4540.752</v>
       </c>
       <c r="I8" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J8" t="n">
-        <v>-1167.844907068292</v>
+        <v>-1412.522263665927</v>
       </c>
       <c r="K8" t="n">
-        <v>-535.1039961575161</v>
+        <v>-290.4266395598809</v>
       </c>
     </row>
     <row r="9">
@@ -808,13 +808,13 @@
         <v>3502.096</v>
       </c>
       <c r="I9" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J9" t="n">
-        <v>-777.8985844876461</v>
+        <v>-1022.575941085281</v>
       </c>
       <c r="K9" t="n">
-        <v>-145.1576735768703</v>
+        <v>99.51968302076489</v>
       </c>
     </row>
     <row r="10">
@@ -851,13 +851,13 @@
         <v>4373.424</v>
       </c>
       <c r="I10" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J10" t="n">
-        <v>-981.69432642313</v>
+        <v>-1226.371683020765</v>
       </c>
       <c r="K10" t="n">
-        <v>-348.9534155123542</v>
+        <v>-104.276058914719</v>
       </c>
     </row>
     <row r="11">
@@ -894,13 +894,13 @@
         <v>4349.632000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J11" t="n">
-        <v>-969.4184554553885</v>
+        <v>-1214.095812053024</v>
       </c>
       <c r="K11" t="n">
-        <v>-336.6775445446128</v>
+        <v>-92.00018794697758</v>
       </c>
     </row>
     <row r="12">
@@ -937,13 +937,13 @@
         <v>4614.956</v>
       </c>
       <c r="I12" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J12" t="n">
-        <v>-1085.113423197324</v>
+        <v>-1329.790779794959</v>
       </c>
       <c r="K12" t="n">
-        <v>-452.372512286548</v>
+        <v>-207.6951556889128</v>
       </c>
     </row>
     <row r="13">
@@ -980,13 +980,13 @@
         <v>3744.3</v>
       </c>
       <c r="I13" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J13" t="n">
-        <v>-617.909036100549</v>
+        <v>-862.5863926981842</v>
       </c>
       <c r="K13" t="n">
-        <v>14.83187481022679</v>
+        <v>259.509231407862</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>3529.02</v>
       </c>
       <c r="I14" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J14" t="n">
-        <v>-449.9193586811944</v>
+        <v>-694.5967152788296</v>
       </c>
       <c r="K14" t="n">
-        <v>182.8215522295814</v>
+        <v>427.4989088272166</v>
       </c>
     </row>
     <row r="15">
@@ -1066,13 +1066,13 @@
         <v>3173.040000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J15" t="n">
-        <v>-145.9958102940985</v>
+        <v>-390.6731668917337</v>
       </c>
       <c r="K15" t="n">
-        <v>486.7451006166773</v>
+        <v>731.4224572143125</v>
       </c>
     </row>
     <row r="16">
@@ -1109,13 +1109,13 @@
         <v>3675.011999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J16" t="n">
-        <v>-234.7339393263551</v>
+        <v>-479.4112959239903</v>
       </c>
       <c r="K16" t="n">
-        <v>398.0069715844207</v>
+        <v>642.6843281820559</v>
       </c>
     </row>
     <row r="17">
@@ -1152,13 +1152,13 @@
         <v>3329.963999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J17" t="n">
-        <v>-223.7020683586134</v>
+        <v>-468.3794249562486</v>
       </c>
       <c r="K17" t="n">
-        <v>409.0388425521624</v>
+        <v>653.7161991497976</v>
       </c>
     </row>
     <row r="18">
@@ -1195,13 +1195,13 @@
         <v>3749.080000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J18" t="n">
-        <v>-492.398713519905</v>
+        <v>-737.0760701175402</v>
       </c>
       <c r="K18" t="n">
-        <v>140.3421973908708</v>
+        <v>385.019553988506</v>
       </c>
     </row>
     <row r="19">
@@ -1238,13 +1238,13 @@
         <v>4141.900000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J19" t="n">
-        <v>-605.0977457779691</v>
+        <v>-849.7751023756043</v>
       </c>
       <c r="K19" t="n">
-        <v>27.6431651328067</v>
+        <v>272.3205217304419</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>4026.228</v>
       </c>
       <c r="I20" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J20" t="n">
-        <v>-610.5628425521622</v>
+        <v>-855.2401991497975</v>
       </c>
       <c r="K20" t="n">
-        <v>22.17806835861353</v>
+        <v>266.8554249562487</v>
       </c>
     </row>
     <row r="21">
@@ -1324,13 +1324,13 @@
         <v>3123.584</v>
       </c>
       <c r="I21" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J21" t="n">
-        <v>-316.3704554553879</v>
+        <v>-561.0478120530231</v>
       </c>
       <c r="K21" t="n">
-        <v>316.3704554553879</v>
+        <v>561.0478120530231</v>
       </c>
     </row>
     <row r="22">
@@ -1367,13 +1367,13 @@
         <v>3622.688000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J22" t="n">
-        <v>-244.6357457779696</v>
+        <v>-489.3131023756048</v>
       </c>
       <c r="K22" t="n">
-        <v>388.1051651328062</v>
+        <v>632.7825217304414</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         <v>3379.656</v>
       </c>
       <c r="I23" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J23" t="n">
-        <v>-146.6924554553885</v>
+        <v>-391.3698120530237</v>
       </c>
       <c r="K23" t="n">
-        <v>486.0484554553873</v>
+        <v>730.7258120530225</v>
       </c>
     </row>
     <row r="24">
@@ -1453,13 +1453,13 @@
         <v>3065.792</v>
       </c>
       <c r="I24" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J24" t="n">
-        <v>124.9538026091281</v>
+        <v>-119.7235539885071</v>
       </c>
       <c r="K24" t="n">
-        <v>757.6947135199039</v>
+        <v>1002.372070117539</v>
       </c>
     </row>
     <row r="25">
@@ -1496,13 +1496,13 @@
         <v>2547.760000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J25" t="n">
-        <v>246.7841897059013</v>
+        <v>2.106833108266073</v>
       </c>
       <c r="K25" t="n">
-        <v>879.525100616677</v>
+        <v>1124.202457214312</v>
       </c>
     </row>
     <row r="26">
@@ -1539,13 +1539,13 @@
         <v>2561.980000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J26" t="n">
-        <v>234.3706413188046</v>
+        <v>-10.30671527883055</v>
       </c>
       <c r="K26" t="n">
-        <v>867.1115522295804</v>
+        <v>1111.788908827216</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1582,13 @@
         <v>2339.748000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J27" t="n">
-        <v>394.1671574478373</v>
+        <v>149.4898008502021</v>
       </c>
       <c r="K27" t="n">
-        <v>1026.908068358613</v>
+        <v>1271.585424956248</v>
       </c>
     </row>
     <row r="28">
@@ -1625,13 +1625,13 @@
         <v>2912.652</v>
       </c>
       <c r="I28" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J28" t="n">
-        <v>79.89218970590281</v>
+        <v>-164.7851668917324</v>
       </c>
       <c r="K28" t="n">
-        <v>712.6331006166786</v>
+        <v>957.3104572143138</v>
       </c>
     </row>
     <row r="29">
@@ -1668,13 +1668,13 @@
         <v>2584.456</v>
       </c>
       <c r="I29" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J29" t="n">
-        <v>159.6204477704184</v>
+        <v>-85.05690882721683</v>
       </c>
       <c r="K29" t="n">
-        <v>792.3613586811941</v>
+        <v>1037.038715278829</v>
       </c>
     </row>
     <row r="30">
@@ -1711,13 +1711,13 @@
         <v>3124.34</v>
       </c>
       <c r="I30" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J30" t="n">
-        <v>-104.4248425521624</v>
+        <v>-349.1021991497976</v>
       </c>
       <c r="K30" t="n">
-        <v>528.3160683586134</v>
+        <v>772.9934249562486</v>
       </c>
     </row>
     <row r="31">
@@ -1754,13 +1754,13 @@
         <v>3432.599999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J31" t="n">
-        <v>-148.2412941650644</v>
+        <v>-392.9186507626996</v>
       </c>
       <c r="K31" t="n">
-        <v>484.4996167457114</v>
+        <v>729.1769733433466</v>
       </c>
     </row>
     <row r="32">
@@ -1797,13 +1797,13 @@
         <v>3407.46</v>
       </c>
       <c r="I32" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J32" t="n">
-        <v>-204.2061328747425</v>
+        <v>-448.8834894723777</v>
       </c>
       <c r="K32" t="n">
-        <v>428.5347780360333</v>
+        <v>673.2121346336685</v>
       </c>
     </row>
     <row r="33">
@@ -1840,13 +1840,13 @@
         <v>2615.7</v>
       </c>
       <c r="I33" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J33" t="n">
-        <v>-33.63161674571035</v>
+        <v>-278.3089733433455</v>
       </c>
       <c r="K33" t="n">
-        <v>599.1092941650654</v>
+        <v>843.7866507627007</v>
       </c>
     </row>
     <row r="34">
@@ -1883,13 +1883,13 @@
         <v>3050.936</v>
       </c>
       <c r="I34" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J34" t="n">
-        <v>8.035609060740796</v>
+        <v>-236.6417475368944</v>
       </c>
       <c r="K34" t="n">
-        <v>640.7765199715166</v>
+        <v>885.4538765691518</v>
       </c>
     </row>
     <row r="35">
@@ -1926,13 +1926,13 @@
         <v>3112.400000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J35" t="n">
-        <v>20.5716090607404</v>
+        <v>-224.1057475368948</v>
       </c>
       <c r="K35" t="n">
-        <v>653.3125199715162</v>
+        <v>897.9898765691514</v>
       </c>
     </row>
     <row r="36">
@@ -1969,13 +1969,13 @@
         <v>2877.936000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J36" t="n">
-        <v>326.2694800284823</v>
+        <v>81.5921234308471</v>
       </c>
       <c r="K36" t="n">
-        <v>959.0103909392581</v>
+        <v>1203.687747536893</v>
       </c>
     </row>
     <row r="37">
@@ -2012,13 +2012,13 @@
         <v>2418.384</v>
       </c>
       <c r="I37" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J37" t="n">
-        <v>273.9505122865475</v>
+        <v>29.27315568891231</v>
       </c>
       <c r="K37" t="n">
-        <v>906.6914231973233</v>
+        <v>1151.368779794959</v>
       </c>
     </row>
     <row r="38">
@@ -2055,13 +2055,13 @@
         <v>2619.036000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J38" t="n">
-        <v>218.056576802676</v>
+        <v>-26.62077979495916</v>
       </c>
       <c r="K38" t="n">
-        <v>850.7974877134518</v>
+        <v>1095.474844311087</v>
       </c>
     </row>
     <row r="39">
@@ -2098,13 +2098,13 @@
         <v>2468.963999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J39" t="n">
-        <v>326.2576090607415</v>
+        <v>81.58025246310626</v>
       </c>
       <c r="K39" t="n">
-        <v>958.9985199715172</v>
+        <v>1203.675876569152</v>
       </c>
     </row>
     <row r="40">
@@ -2141,13 +2141,13 @@
         <v>2495.648</v>
       </c>
       <c r="I40" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J40" t="n">
-        <v>285.5816735768698</v>
+        <v>40.90431697923464</v>
       </c>
       <c r="K40" t="n">
-        <v>918.3225844876456</v>
+        <v>1162.999941085281</v>
       </c>
     </row>
     <row r="41">
@@ -2184,13 +2184,13 @@
         <v>2823.384</v>
       </c>
       <c r="I41" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J41" t="n">
-        <v>101.6198671252575</v>
+        <v>-143.0574894723777</v>
       </c>
       <c r="K41" t="n">
-        <v>734.3607780360333</v>
+        <v>979.0381346336685</v>
       </c>
     </row>
     <row r="42">
@@ -2227,13 +2227,13 @@
         <v>3010.348000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J42" t="n">
-        <v>-51.86026190700187</v>
+        <v>-296.5376185046371</v>
       </c>
       <c r="K42" t="n">
-        <v>580.8806490037739</v>
+        <v>825.5580056014091</v>
       </c>
     </row>
     <row r="43">
@@ -2270,13 +2270,13 @@
         <v>3180.672</v>
       </c>
       <c r="I43" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J43" t="n">
-        <v>1.05767357686949</v>
+        <v>-243.6196830207657</v>
       </c>
       <c r="K43" t="n">
-        <v>633.7985844876453</v>
+        <v>878.4759410852805</v>
       </c>
     </row>
     <row r="44">
@@ -2313,13 +2313,13 @@
         <v>3656.06</v>
       </c>
       <c r="I44" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J44" t="n">
-        <v>-305.257745777969</v>
+        <v>-549.9351023756042</v>
       </c>
       <c r="K44" t="n">
-        <v>327.4831651328068</v>
+        <v>572.160521730442</v>
       </c>
     </row>
     <row r="45">
@@ -2356,13 +2356,13 @@
         <v>2493.703999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J45" t="n">
-        <v>60.25954454461265</v>
+        <v>-184.4178120530225</v>
       </c>
       <c r="K45" t="n">
-        <v>693.0004554553884</v>
+        <v>937.6778120530237</v>
       </c>
     </row>
     <row r="46">
@@ -2399,13 +2399,13 @@
         <v>3142.816</v>
       </c>
       <c r="I46" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J46" t="n">
-        <v>-45.34439093925886</v>
+        <v>-290.0217475368941</v>
       </c>
       <c r="K46" t="n">
-        <v>587.3965199715169</v>
+        <v>832.0738765691522</v>
       </c>
     </row>
     <row r="47">
@@ -2442,13 +2442,13 @@
         <v>3434.048</v>
       </c>
       <c r="I47" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J47" t="n">
-        <v>-195.7538102940978</v>
+        <v>-440.431166891733</v>
       </c>
       <c r="K47" t="n">
-        <v>436.987100616678</v>
+        <v>681.6644572143132</v>
       </c>
     </row>
     <row r="48">
@@ -2485,13 +2485,13 @@
         <v>2786.708</v>
       </c>
       <c r="I48" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J48" t="n">
-        <v>185.9168348671926</v>
+        <v>-58.76052173044263</v>
       </c>
       <c r="K48" t="n">
-        <v>818.6577457779683</v>
+        <v>1063.335102375604</v>
       </c>
     </row>
     <row r="49">
@@ -2528,13 +2528,13 @@
         <v>2530.692</v>
       </c>
       <c r="I49" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J49" t="n">
-        <v>241.0699316413861</v>
+        <v>-3.607424956249133</v>
       </c>
       <c r="K49" t="n">
-        <v>873.8108425521618</v>
+        <v>1118.488199149797</v>
       </c>
     </row>
     <row r="50">
@@ -2571,13 +2571,13 @@
         <v>2639.432</v>
       </c>
       <c r="I50" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J50" t="n">
-        <v>194.7896090607407</v>
+        <v>-49.88774753689449</v>
       </c>
       <c r="K50" t="n">
-        <v>827.5305199715165</v>
+        <v>1072.207876569152</v>
       </c>
     </row>
     <row r="51">
@@ -2614,13 +2614,13 @@
         <v>2381.971999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J51" t="n">
-        <v>341.4996090607416</v>
+        <v>96.82225246310645</v>
       </c>
       <c r="K51" t="n">
-        <v>974.2405199715174</v>
+        <v>1218.917876569153</v>
       </c>
     </row>
     <row r="52">
@@ -2657,13 +2657,13 @@
         <v>2602.26</v>
       </c>
       <c r="I52" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J52" t="n">
-        <v>268.3083832542893</v>
+        <v>23.63102665665406</v>
       </c>
       <c r="K52" t="n">
-        <v>901.049294165065</v>
+        <v>1145.7266507627</v>
       </c>
     </row>
     <row r="53">
@@ -2700,13 +2700,13 @@
         <v>2581.472</v>
       </c>
       <c r="I53" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J53" t="n">
-        <v>204.2657380929992</v>
+        <v>-40.41161850463595</v>
       </c>
       <c r="K53" t="n">
-        <v>837.006649003775</v>
+        <v>1081.68400560141</v>
       </c>
     </row>
     <row r="54">
@@ -2743,13 +2743,13 @@
         <v>3022.759999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J54" t="n">
-        <v>-72.09484255216108</v>
+        <v>-316.7721991497963</v>
       </c>
       <c r="K54" t="n">
-        <v>560.6460683586147</v>
+        <v>805.3234249562499</v>
       </c>
     </row>
     <row r="55">
@@ -2786,13 +2786,13 @@
         <v>3466.591999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J55" t="n">
-        <v>-160.5397457779673</v>
+        <v>-405.2171023756025</v>
       </c>
       <c r="K55" t="n">
-        <v>472.2011651328085</v>
+        <v>716.8785217304437</v>
       </c>
     </row>
     <row r="56">
@@ -2829,13 +2829,13 @@
         <v>3875.528</v>
       </c>
       <c r="I56" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J56" t="n">
-        <v>-500.9273586811947</v>
+        <v>-745.6047152788299</v>
       </c>
       <c r="K56" t="n">
-        <v>131.8135522295811</v>
+        <v>376.4909088272163</v>
       </c>
     </row>
     <row r="57">
@@ -2872,13 +2872,13 @@
         <v>2531.836</v>
       </c>
       <c r="I57" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J57" t="n">
-        <v>17.73238325428969</v>
+        <v>-226.9449733433455</v>
       </c>
       <c r="K57" t="n">
-        <v>650.4732941650655</v>
+        <v>895.1506507627007</v>
       </c>
     </row>
     <row r="58">
@@ -2915,13 +2915,13 @@
         <v>3418.488000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J58" t="n">
-        <v>-151.9196167457113</v>
+        <v>-396.5969733433465</v>
       </c>
       <c r="K58" t="n">
-        <v>480.8212941650646</v>
+        <v>725.4986507626998</v>
       </c>
     </row>
     <row r="59">
@@ -2958,13 +2958,13 @@
         <v>3391.068</v>
       </c>
       <c r="I59" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J59" t="n">
-        <v>-155.1851006166781</v>
+        <v>-399.8624572143133</v>
       </c>
       <c r="K59" t="n">
-        <v>477.5558102940977</v>
+        <v>722.2331668917329</v>
       </c>
     </row>
     <row r="60">
@@ -3001,13 +3001,13 @@
         <v>2871.248000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J60" t="n">
-        <v>121.7478026091275</v>
+        <v>-122.9295539885077</v>
       </c>
       <c r="K60" t="n">
-        <v>754.4887135199033</v>
+        <v>999.1660701175385</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>2701.280000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J61" t="n">
-        <v>140.5625768026759</v>
+        <v>-104.1147797949593</v>
       </c>
       <c r="K61" t="n">
-        <v>773.3034877134517</v>
+        <v>1017.980844311087</v>
       </c>
     </row>
     <row r="62">
@@ -3087,13 +3087,13 @@
         <v>2618.092000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J62" t="n">
-        <v>123.1779961575145</v>
+        <v>-121.4993604401207</v>
       </c>
       <c r="K62" t="n">
-        <v>755.9189070682903</v>
+        <v>1000.596263665926</v>
       </c>
     </row>
     <row r="63">
@@ -3130,13 +3130,13 @@
         <v>2477.000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J63" t="n">
-        <v>253.0764477704176</v>
+        <v>8.399091172782391</v>
       </c>
       <c r="K63" t="n">
-        <v>885.8173586811934</v>
+        <v>1130.494715278829</v>
       </c>
     </row>
     <row r="64">
@@ -3173,13 +3173,13 @@
         <v>2940.676</v>
       </c>
       <c r="I64" t="n">
-        <v>161.4134976813204</v>
+        <v>286.248883700522</v>
       </c>
       <c r="J64" t="n">
-        <v>28.69077035106324</v>
+        <v>-215.986586246572</v>
       </c>
       <c r="K64" t="n">
-        <v>661.431681261839</v>
+        <v>906.1090378594743</v>
       </c>
     </row>
   </sheetData>
